--- a/files/九龙-马头角-南首.xlsx
+++ b/files/九龙-马头角-南首.xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -905,7 +905,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -967,7 +967,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6795,7 +6795,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8345,7 +8345,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8407,7 +8407,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8469,7 +8469,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8593,7 +8593,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9213,7 +9213,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -9895,7 +9895,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -9957,7 +9957,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10019,7 +10019,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10081,7 +10081,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10205,7 +10205,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10453,7 +10453,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10515,7 +10515,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10577,7 +10577,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10763,7 +10763,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -10887,7 +10887,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11073,7 +11073,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11197,7 +11197,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11259,7 +11259,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11569,7 +11569,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11755,7 +11755,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -11817,7 +11817,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -11941,7 +11941,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12065,7 +12065,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12251,7 +12251,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12313,7 +12313,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12375,7 +12375,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -12623,7 +12623,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12685,7 +12685,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -12747,7 +12747,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -12933,7 +12933,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -12995,7 +12995,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13057,7 +13057,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13181,7 +13181,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13243,7 +13243,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13305,7 +13305,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13367,7 +13367,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13429,7 +13429,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13553,7 +13553,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13615,7 +13615,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -13677,7 +13677,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -13739,7 +13739,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -13801,7 +13801,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -13863,7 +13863,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -13925,7 +13925,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -13987,7 +13987,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14173,7 +14173,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14235,7 +14235,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14297,7 +14297,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14359,7 +14359,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14483,7 +14483,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14545,7 +14545,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -14607,7 +14607,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -14669,7 +14669,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -14731,7 +14731,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -14855,7 +14855,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -14917,7 +14917,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -14979,7 +14979,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15103,7 +15103,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15165,7 +15165,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15227,7 +15227,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15289,7 +15289,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15351,7 +15351,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -15413,7 +15413,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15475,7 +15475,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -15537,7 +15537,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -15661,7 +15661,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -15723,7 +15723,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -15785,7 +15785,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -15847,7 +15847,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -15909,7 +15909,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -15971,7 +15971,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16095,7 +16095,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16157,7 +16157,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16219,7 +16219,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16281,7 +16281,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16343,7 +16343,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -16405,7 +16405,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -16529,7 +16529,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -16591,7 +16591,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -16715,7 +16715,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -16777,7 +16777,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -16839,7 +16839,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -16963,7 +16963,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -17025,7 +17025,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -17087,7 +17087,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -17149,7 +17149,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -17211,7 +17211,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -17273,7 +17273,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -17335,7 +17335,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -17397,7 +17397,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -17459,7 +17459,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -17583,7 +17583,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -17645,7 +17645,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -17707,7 +17707,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -17769,7 +17769,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -17831,7 +17831,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -17893,7 +17893,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -17955,7 +17955,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -18017,7 +18017,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -18079,7 +18079,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -18141,7 +18141,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -18203,7 +18203,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -18265,7 +18265,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -18327,7 +18327,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -18389,7 +18389,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -18451,7 +18451,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -18513,7 +18513,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -18575,7 +18575,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -18637,7 +18637,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -18699,7 +18699,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -18761,7 +18761,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -18823,7 +18823,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -18885,7 +18885,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -18947,7 +18947,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -19009,7 +19009,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -19071,7 +19071,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -19133,7 +19133,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -19195,7 +19195,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -19257,7 +19257,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -19319,7 +19319,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -19381,7 +19381,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -19443,7 +19443,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -19505,7 +19505,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -19567,7 +19567,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -19629,7 +19629,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -19691,7 +19691,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -19753,7 +19753,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -19815,7 +19815,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -19877,7 +19877,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -19939,7 +19939,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -20001,7 +20001,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -20063,7 +20063,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -20125,7 +20125,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -20356,7 +20356,7 @@
           <t>A1 | 353呎 (2房)
 $1120万
 $31,728/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -20364,7 +20364,7 @@
           <t>A2 | 342呎 (2房)
 $868万
 $25,374/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -20372,7 +20372,7 @@
           <t>A3 | 263呎 (1房)
 $653万
 $24,820/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -20380,7 +20380,7 @@
           <t>A5 | 258呎 (1房)
 $638万
 $24,728/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -20388,7 +20388,7 @@
           <t>A6 | 200呎 (开放式)
 $464万
 $23,182/呎
-(26年-07月-21日)</t>
+(26年-07月-22日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -20396,7 +20396,7 @@
           <t>A7 | 262呎 (1房)
 $617万
 $23,565/呎
-(26年-07月-19日)</t>
+(26年-07月-20日)</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr"/>
@@ -20405,7 +20405,7 @@
           <t>B1 | 358呎 (2房)
 $1039万
 $29,017/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="J5" s="20" t="inlineStr">
@@ -20413,7 +20413,7 @@
           <t>B2 | 342呎 (2房)
 $882万
 $25,781/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="K5" s="22" t="inlineStr">
@@ -20429,7 +20429,7 @@
           <t>B5 | 263呎 (1房)
 $668万
 $25,383/呎
-(26年-07月-19日)</t>
+(26年-07月-20日)</t>
         </is>
       </c>
       <c r="M5" s="20" t="inlineStr">
@@ -20437,7 +20437,7 @@
           <t>B6 | 258呎 (1房)
 $655万
 $25,404/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="N5" s="20" t="inlineStr">
@@ -20445,7 +20445,7 @@
           <t>B7 | 200呎 (开放式)
 $457万
 $22,838/呎
-(26年-07月-19日)</t>
+(26年-07月-20日)</t>
         </is>
       </c>
       <c r="O5" s="22" t="inlineStr">
@@ -20469,7 +20469,7 @@
           <t>A1 | 349呎 (2房)
 $886万
 $25,399/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -20477,7 +20477,7 @@
           <t>A2 | 342呎 (2房)
 $798万
 $23,320/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -20485,7 +20485,7 @@
           <t>A3 | 263呎 (1房)
 $646万
 $24,556/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -20493,7 +20493,7 @@
           <t>A5 | 258呎 (1房)
 $631万
 $24,462/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -20501,7 +20501,7 @@
           <t>A6 | 200呎 (开放式)
 $400万
 $19,987/呎
-(25年-04月-14日)</t>
+(25年-04月-15日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -20509,7 +20509,7 @@
           <t>A7 | 262呎 (1房)
 $611万
 $23,310/呎
-(26年-07月-18日)</t>
+(26年-07月-19日)</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
@@ -20525,7 +20525,7 @@
           <t>B1 | 351呎 (2房)
 $905万
 $25,795/呎
-(26年-07月-17日)</t>
+(26年-07月-18日)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -20533,7 +20533,7 @@
           <t>B2 | 342呎 (2房)
 $803万
 $23,471/呎
-(25年-11月-19日)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr">
@@ -20541,7 +20541,7 @@
           <t>B3 | 263呎 (1房)
 $654万
 $24,884/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="L6" s="20" t="inlineStr">
@@ -20549,7 +20549,7 @@
           <t>B5 | 263呎 (1房)
 $654万
 $24,884/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="M6" s="20" t="inlineStr">
@@ -20557,7 +20557,7 @@
           <t>B6 | 258呎 (1房)
 $648万
 $25,130/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="N6" s="20" t="inlineStr">
@@ -20565,7 +20565,7 @@
           <t>B7 | 200呎 (开放式)
 $400万
 $19,982/呎
-(25年-04月-27日)</t>
+(25年-04月-28日)</t>
         </is>
       </c>
       <c r="O6" s="24" t="inlineStr">
@@ -20596,7 +20596,7 @@
           <t>A1 | 349呎 (2房)
 $870万
 $24,924/呎
-(26年-05月-04日)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -20604,7 +20604,7 @@
           <t>A2 | 342呎 (2房)
 $776万
 $22,677/呎
-(25年-03月-30日)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -20612,7 +20612,7 @@
           <t>A3 | 263呎 (1房)
 $584万
 $22,188/呎
-(25年-05月-11日)</t>
+(25年-05月-12日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -20620,7 +20620,7 @@
           <t>A5 | 258呎 (1房)
 $571万
 $22,130/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -20628,7 +20628,7 @@
           <t>A6 | 200呎 (开放式)
 $399万
 $19,950/呎
-(25年-04月-08日)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -20636,7 +20636,7 @@
           <t>A7 | 262呎 (1房)
 $603万
 $23,030/呎
-(26年-07月-21日)</t>
+(26年-07月-22日)</t>
         </is>
       </c>
       <c r="H7" s="22" t="inlineStr">
@@ -20652,7 +20652,7 @@
           <t>B1 | 351呎 (2房)
 $888万
 $25,301/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -20660,7 +20660,7 @@
           <t>B2 | 342呎 (2房)
 $781万
 $22,836/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="K7" s="20" t="inlineStr">
@@ -20668,7 +20668,7 @@
           <t>B3 | 263呎 (1房)
 $650万
 $24,697/呎
-(26年-04月-10日)</t>
+(26年-04月-11日)</t>
         </is>
       </c>
       <c r="L7" s="20" t="inlineStr">
@@ -20676,7 +20676,7 @@
           <t>B5 | 263呎 (1房)
 $650万
 $24,697/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="M7" s="20" t="inlineStr">
@@ -20684,7 +20684,7 @@
           <t>B6 | 258呎 (1房)
 $638万
 $24,735/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="N7" s="20" t="inlineStr">
@@ -20692,7 +20692,7 @@
           <t>B7 | 200呎 (开放式)
 $399万
 $19,964/呎
-(25年-05月-07日)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
       <c r="O7" s="22" t="inlineStr">
@@ -20708,7 +20708,7 @@
           <t>B9 | 261呎 (1房)
 $590万
 $22,612/呎
-(25年-07月-22日)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
     </row>
@@ -20723,7 +20723,7 @@
           <t>A1 | 349呎 (2房)
 $787万
 $22,549/呎
-(25年-10月-27日)</t>
+(25年-10月-28日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -20731,7 +20731,7 @@
           <t>A2 | 342呎 (2房)
 $756万
 $22,096/呎
-(25年-03月-30日)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -20739,7 +20739,7 @@
           <t>A3 | 263呎 (1房)
 $570万
 $21,667/呎
-(25年-03月-31日)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -20747,7 +20747,7 @@
           <t>A5 | 258呎 (1房)
 $558万
 $21,631/呎
-(25年-06月-12日)</t>
+(25年-06月-13日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -20755,7 +20755,7 @@
           <t>A6 | 200呎 (开放式)
 $406万
 $20,322/呎
-(25年-03月-31日)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -20763,7 +20763,7 @@
           <t>A7 | 262呎 (1房)
 $542万
 $20,686/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr">
@@ -20779,7 +20779,7 @@
           <t>B1 | 351呎 (2房)
 $810万
 $23,084/呎
-(25年-08月-26日)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -20787,7 +20787,7 @@
           <t>B2 | 342呎 (2房)
 $761万
 $22,257/呎
-(25年-03月-27日)</t>
+(25年-03月-28日)</t>
         </is>
       </c>
       <c r="K8" s="20" t="inlineStr">
@@ -20795,7 +20795,7 @@
           <t>B3 | 263呎 (1房)
 $637万
 $24,232/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="L8" s="20" t="inlineStr">
@@ -20803,7 +20803,7 @@
           <t>B5 | 263呎 (1房)
 $637万
 $24,232/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="M8" s="20" t="inlineStr">
@@ -20811,7 +20811,7 @@
           <t>B6 | 258呎 (1房)
 $558万
 $21,631/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="N8" s="20" t="inlineStr">
@@ -20819,7 +20819,7 @@
           <t>B7 | 200呎 (开放式)
 $399万
 $19,936/呎
-(25年-03月-31日)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
       <c r="O8" s="20" t="inlineStr">
@@ -20827,7 +20827,7 @@
           <t>B8 | 262呎 (1房)
 $568万
 $21,673/呎
-(25年-03月-27日)</t>
+(25年-03月-28日)</t>
         </is>
       </c>
       <c r="P8" s="20" t="inlineStr">
@@ -20835,7 +20835,7 @@
           <t>B9 | 261呎 (1房)
 $576万
 $22,087/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
     </row>
@@ -20850,7 +20850,7 @@
           <t>A1 | 349呎 (2房)
 $768万
 $22,009/呎
-(25年-11月-02日)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -20858,7 +20858,7 @@
           <t>A2 | 342呎 (2房)
 $703万
 $20,541/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -20866,7 +20866,7 @@
           <t>A3 | 263呎 (1房)
 $556万
 $21,142/呎
-(25年-04月-09日)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -20874,7 +20874,7 @@
           <t>A5 | 258呎 (1房)
 $545万
 $21,135/呎
-(25年-03月-27日)</t>
+(25年-03月-28日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -20882,7 +20882,7 @@
           <t>A6 | 200呎 (开放式)
 $395万
 $19,734/呎
-(25年-04月-06日)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -20890,7 +20890,7 @@
           <t>A7 | 262呎 (1房)
 $530万
 $20,244/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -20898,7 +20898,7 @@
           <t>A8 | 262呎 (1房)
 $650万
 $24,806/呎
-(26年-07月-13日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -20906,7 +20906,7 @@
           <t>B1 | 351呎 (2房)
 $791万
 $22,523/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -20914,7 +20914,7 @@
           <t>B2 | 342呎 (2房)
 $715万
 $20,902/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="K9" s="20" t="inlineStr">
@@ -20922,7 +20922,7 @@
           <t>B3 | 263呎 (1房)
 $630万
 $23,967/呎
-(26年-05月-04日)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="L9" s="20" t="inlineStr">
@@ -20930,7 +20930,7 @@
           <t>B5 | 263呎 (1房)
 $630万
 $23,967/呎
-(26年-05月-04日)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="M9" s="20" t="inlineStr">
@@ -20938,7 +20938,7 @@
           <t>B6 | 258呎 (1房)
 $545万
 $21,135/呎
-(25年-04月-13日)</t>
+(25年-04月-14日)</t>
         </is>
       </c>
       <c r="N9" s="20" t="inlineStr">
@@ -20946,7 +20946,7 @@
           <t>B7 | 200呎 (开放式)
 $397万
 $19,867/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="O9" s="20" t="inlineStr">
@@ -20954,7 +20954,7 @@
           <t>B8 | 262呎 (1房)
 $572万
 $21,839/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="P9" s="20" t="inlineStr">
@@ -20962,7 +20962,7 @@
           <t>B9 | 261呎 (1房)
 $563万
 $21,562/呎
-(25年-03月-31日)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
     </row>
@@ -20977,7 +20977,7 @@
           <t>A1 | 349呎 (2房)
 $723万
 $20,707/呎
-(25年-03月-17日)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -20985,7 +20985,7 @@
           <t>A2 | 342呎 (2房)
 $702万
 $20,520/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -20993,7 +20993,7 @@
           <t>A3 | 263呎 (1房)
 $542万
 $20,617/呎
-(25年-03月-27日)</t>
+(25年-03月-28日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -21001,7 +21001,7 @@
           <t>A5 | 258呎 (1房)
 $544万
 $21,081/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -21009,7 +21009,7 @@
           <t>A6 | 200呎 (开放式)
 $402万
 $20,088/呎
-(25年-04月-09日)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -21017,7 +21017,7 @@
           <t>A7 | 262呎 (1房)
 $510万
 $19,469/呎
-(25年-03月-31日)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -21025,7 +21025,7 @@
           <t>A8 | 262呎 (1房)
 $640万
 $24,425/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -21033,7 +21033,7 @@
           <t>B1 | 351呎 (2房)
 $773万
 $22,025/呎
-(25年-04月-07日)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -21041,7 +21041,7 @@
           <t>B2 | 342呎 (2房)
 $700万
 $20,458/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="K10" s="20" t="inlineStr">
@@ -21049,7 +21049,7 @@
           <t>B3 | 263呎 (1房)
 $556万
 $21,129/呎
-(25年-04月-24日)</t>
+(25年-04月-25日)</t>
         </is>
       </c>
       <c r="L10" s="20" t="inlineStr">
@@ -21057,7 +21057,7 @@
           <t>B5 | 263呎 (1房)
 $556万
 $21,129/呎
-(25年-04月-07日)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="M10" s="20" t="inlineStr">
@@ -21065,7 +21065,7 @@
           <t>B6 | 258呎 (1房)
 $532万
 $20,632/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="N10" s="20" t="inlineStr">
@@ -21073,7 +21073,7 @@
           <t>B7 | 200呎 (开放式)
 $396万
 $19,816/呎
-(25年-04月-07日)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="O10" s="20" t="inlineStr">
@@ -21081,7 +21081,7 @@
           <t>B8 | 262呎 (1房)
 $552万
 $21,071/呎
-(25年-03月-31日)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
       <c r="P10" s="20" t="inlineStr">
@@ -21089,7 +21089,7 @@
           <t>B9 | 261呎 (1房)
 $561万
 $21,494/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
     </row>
@@ -21104,7 +21104,7 @@
           <t>A1 | 349呎 (2房)
 $709万
 $20,306/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -21112,7 +21112,7 @@
           <t>A2 | 342呎 (2房)
 $674万
 $19,710/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -21120,7 +21120,7 @@
           <t>A3 | 263呎 (1房)
 $537万
 $20,402/呎
-(25年-03月-27日)</t>
+(25年-03月-28日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -21128,7 +21128,7 @@
           <t>A5 | 258呎 (1房)
 $521万
 $20,206/呎
-(25年-03月-17日)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -21136,7 +21136,7 @@
           <t>A6 | 200呎 (开放式)
 $392万
 $19,614/呎
-(25年-04月-07日)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -21144,7 +21144,7 @@
           <t>A7 | 262呎 (1房)
 $497万
 $18,958/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -21152,7 +21152,7 @@
           <t>A8 | 262呎 (1房)
 $568万
 $21,677/呎
-(25年-03月-07日)</t>
+(25年-03月-08日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -21160,7 +21160,7 @@
           <t>B1 | 351呎 (2房)
 $729万
 $20,759/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -21168,7 +21168,7 @@
           <t>B2 | 342呎 (2房)
 $686万
 $20,068/呎
-(25年-03月-18日)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr">
@@ -21176,7 +21176,7 @@
           <t>B3 | 263呎 (1房)
 $527万
 $20,054/呎
-(25年-03月-17日)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="L11" s="20" t="inlineStr">
@@ -21184,7 +21184,7 @@
           <t>B5 | 263呎 (1房)
 $539万
 $20,490/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="M11" s="20" t="inlineStr">
@@ -21192,7 +21192,7 @@
           <t>B6 | 258呎 (1房)
 $511万
 $19,798/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="N11" s="20" t="inlineStr">
@@ -21200,7 +21200,7 @@
           <t>B7 | 200呎 (开放式)
 $395万
 $19,743/呎
-(25年-04月-07日)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="O11" s="20" t="inlineStr">
@@ -21208,7 +21208,7 @@
           <t>B8 | 262呎 (1房)
 $528万
 $20,159/呎
-(25年-03月-27日)</t>
+(25年-03月-28日)</t>
         </is>
       </c>
       <c r="P11" s="20" t="inlineStr">
@@ -21216,7 +21216,7 @@
           <t>B9 | 261呎 (1房)
 $529万
 $20,264/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
     </row>
@@ -21231,7 +21231,7 @@
           <t>A1 | 349呎 (2房)
 $697万
 $19,960/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -21239,7 +21239,7 @@
           <t>A2 | 342呎 (2房)
 $663万
 $19,376/呎
-(25年-03月-27日)</t>
+(25年-03月-28日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -21247,7 +21247,7 @@
           <t>A3 | 263呎 (1房)
 $509万
 $19,358/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -21255,7 +21255,7 @@
           <t>A5 | 258呎 (1房)
 $512万
 $19,838/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -21263,7 +21263,7 @@
           <t>A6 | 200呎 (开放式)
 $400万
 $19,989/呎
-(25年-04月-09日)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -21271,7 +21271,7 @@
           <t>A7 | 262呎 (1房)
 $504万
 $19,253/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -21279,7 +21279,7 @@
           <t>A8 | 262呎 (1房)
 $541万
 $20,637/呎
-(25年-02月-28日)</t>
+(25年-03月-01日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -21287,7 +21287,7 @@
           <t>B1 | 351呎 (2房)
 $716万
 $20,400/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -21295,7 +21295,7 @@
           <t>B2 | 342呎 (2房)
 $675万
 $19,734/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr">
@@ -21303,7 +21303,7 @@
           <t>B3 | 263呎 (1房)
 $528万
 $20,083/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="L12" s="20" t="inlineStr">
@@ -21311,7 +21311,7 @@
           <t>B5 | 263呎 (1房)
 $528万
 $20,083/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="M12" s="20" t="inlineStr">
@@ -21319,7 +21319,7 @@
           <t>B6 | 258呎 (1房)
 $501万
 $19,416/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="N12" s="20" t="inlineStr">
@@ -21327,7 +21327,7 @@
           <t>B7 | 200呎 (开放式)
 $390万
 $19,513/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="O12" s="20" t="inlineStr">
@@ -21335,7 +21335,7 @@
           <t>B8 | 262呎 (1房)
 $507万
 $19,362/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="P12" s="20" t="inlineStr">
@@ -21343,7 +21343,7 @@
           <t>B9 | 261呎 (1房)
 $518万
 $19,863/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
     </row>
@@ -21358,7 +21358,7 @@
           <t>A1 | 349呎 (2房)
 $700万
 $20,044/呎
-(25年-03月-18日)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -21366,7 +21366,7 @@
           <t>A2 | 342呎 (2房)
 $651万
 $19,027/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -21374,7 +21374,7 @@
           <t>A3 | 263呎 (1房)
 $500万
 $18,998/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -21382,7 +21382,7 @@
           <t>A5 | 258呎 (1房)
 $493万
 $19,091/呎
-(25年-03月-18日)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -21390,7 +21390,7 @@
           <t>A6 | 200呎 (开放式)
 $390万
 $19,504/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -21398,7 +21398,7 @@
           <t>A7 | 262呎 (1房)
 $499万
 $19,032/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -21406,7 +21406,7 @@
           <t>A8 | 262呎 (1房)
 $553万
 $21,114/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -21414,7 +21414,7 @@
           <t>B1 | 351呎 (2房)
 $703万
 $20,041/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -21422,7 +21422,7 @@
           <t>B2 | 342呎 (2房)
 $678万
 $19,822/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
@@ -21430,7 +21430,7 @@
           <t>B3 | 263呎 (1房)
 $524万
 $19,943/呎
-(25年-02月-28日)</t>
+(25年-03月-01日)</t>
         </is>
       </c>
       <c r="L13" s="20" t="inlineStr">
@@ -21438,7 +21438,7 @@
           <t>B5 | 263呎 (1房)
 $519万
 $19,733/呎
-(25年-03月-27日)</t>
+(25年-03月-28日)</t>
         </is>
       </c>
       <c r="M13" s="20" t="inlineStr">
@@ -21446,7 +21446,7 @@
           <t>B6 | 258呎 (1房)
 $503万
 $19,507/呎
-(25年-03月-17日)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="N13" s="20" t="inlineStr">
@@ -21454,7 +21454,7 @@
           <t>B7 | 200呎 (开放式)
 $389万
 $19,467/呎
-(25年-03月-30日)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
       <c r="O13" s="20" t="inlineStr">
@@ -21462,7 +21462,7 @@
           <t>B8 | 262呎 (1房)
 $498万
 $19,018/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="P13" s="20" t="inlineStr">
@@ -21470,7 +21470,7 @@
           <t>B9 | 261呎 (1房)
 $509万
 $19,517/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
     </row>
@@ -21485,7 +21485,7 @@
           <t>A1 | 349呎 (2房)
 $675万
 $19,330/呎
-(25年-03月-27日)</t>
+(25年-03月-28日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -21493,7 +21493,7 @@
           <t>A2 | 342呎 (2房)
 $656万
 $19,171/呎
-(25年-03月-18日)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -21501,7 +21501,7 @@
           <t>A3 | 263呎 (1房)
 $509万
 $19,343/呎
-(25年-02月-28日)</t>
+(25年-03月-01日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -21509,7 +21509,7 @@
           <t>A5 | 258呎 (1房)
 $486万
 $18,821/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -21517,7 +21517,7 @@
           <t>A6 | 200呎 (开放式)
 $385万
 $19,274/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -21525,7 +21525,7 @@
           <t>A7 | 262呎 (1房)
 $493万
 $18,814/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -21533,7 +21533,7 @@
           <t>A8 | 262呎 (1房)
 $524万
 $19,991/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -21541,7 +21541,7 @@
           <t>B1 | 351呎 (2房)
 $693万
 $19,742/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -21549,7 +21549,7 @@
           <t>B2 | 342呎 (2房)
 $661万
 $19,331/呎
-(25年-03月-18日)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr">
@@ -21557,7 +21557,7 @@
           <t>B3 | 263呎 (1房)
 $500万
 $19,030/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="L14" s="20" t="inlineStr">
@@ -21565,7 +21565,7 @@
           <t>B5 | 263呎 (1房)
 $500万
 $19,030/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="M14" s="20" t="inlineStr">
@@ -21573,7 +21573,7 @@
           <t>B6 | 258呎 (1房)
 $486万
 $18,821/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">
@@ -21581,7 +21581,7 @@
           <t>B7 | 200呎 (开放式)
 $385万
 $19,237/呎
-(25年-04月-14日)</t>
+(25年-04月-15日)</t>
         </is>
       </c>
       <c r="O14" s="20" t="inlineStr">
@@ -21589,7 +21589,7 @@
           <t>B8 | 262呎 (1房)
 $491万
 $18,730/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="P14" s="20" t="inlineStr">
@@ -21597,7 +21597,7 @@
           <t>B9 | 261呎 (1房)
 $513万
 $19,650/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
     </row>
@@ -21612,7 +21612,7 @@
           <t>A1 | 349呎 (2房)
 $681万
 $19,516/呎
-(25年-03月-18日)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -21620,7 +21620,7 @@
           <t>A2 | 342呎 (2房)
 $655万
 $19,147/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -21628,7 +21628,7 @@
           <t>A3 | 263呎 (1房)
 $503万
 $19,108/呎
-(25年-03月-18日)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -21636,7 +21636,7 @@
           <t>A5 | 258呎 (1房)
 $490万
 $19,007/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -21644,7 +21644,7 @@
           <t>A6 | 200呎 (开放式)
 $393万
 $19,646/呎
-(25年-04月-06日)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -21652,7 +21652,7 @@
           <t>A7 | 262呎 (1房)
 $473万
 $18,052/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -21660,7 +21660,7 @@
           <t>A8 | 262呎 (1房)
 $518万
 $19,758/呎
-(25年-03月-17日)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -21668,7 +21668,7 @@
           <t>B1 | 351呎 (2房)
 $685万
 $19,503/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -21676,7 +21676,7 @@
           <t>B2 | 342呎 (2房)
 $646万
 $18,903/呎
-(25年-03月-17日)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="K15" s="20" t="inlineStr">
@@ -21684,7 +21684,7 @@
           <t>B3 | 263呎 (1房)
 $494万
 $18,798/呎
-(25年-03月-17日)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="L15" s="20" t="inlineStr">
@@ -21692,7 +21692,7 @@
           <t>B5 | 263呎 (1房)
 $494万
 $18,798/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="M15" s="20" t="inlineStr">
@@ -21700,7 +21700,7 @@
           <t>B6 | 258呎 (1房)
 $490万
 $19,007/呎
-(25年-03月-18日)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="N15" s="20" t="inlineStr">
@@ -21708,7 +21708,7 @@
           <t>B7 | 200呎 (开放式)
 $380万
 $19,007/呎
-(25年-04月-08日)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="O15" s="20" t="inlineStr">
@@ -21716,7 +21716,7 @@
           <t>B8 | 262呎 (1房)
 $485万
 $18,502/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="P15" s="20" t="inlineStr">
@@ -21724,7 +21724,7 @@
           <t>B9 | 261呎 (1房)
 $496万
 $19,003/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
     </row>
@@ -21739,7 +21739,7 @@
           <t>A1 | 349呎 (2房)
 $661万
 $18,930/呎
-(25年-03月-17日)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -21747,7 +21747,7 @@
           <t>A2 | 342呎 (2房)
 $628万
 $18,376/呎
-(25年-02月-28日)</t>
+(25年-03月-01日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -21755,7 +21755,7 @@
           <t>A3 | 263呎 (1房)
 $493万
 $18,732/呎
-(25年-04月-02日)</t>
+(25年-04月-03日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -21763,7 +21763,7 @@
           <t>A5 | 258呎 (1房)
 $476万
 $18,439/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -21771,7 +21771,7 @@
           <t>A6 | 200呎 (开放式)
 $381万
 $19,053/呎
-(25年-04月-07日)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -21779,7 +21779,7 @@
           <t>A7 | 262呎 (1房)
 $469万
 $17,891/呎
-(25年-03月-13日)</t>
+(25年-03月-14日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -21787,7 +21787,7 @@
           <t>A8 | 262呎 (1房)
 $502万
 $19,165/呎
-(25年-02月-28日)</t>
+(25年-03月-01日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -21795,7 +21795,7 @@
           <t>B1 | 351呎 (2房)
 $678万
 $19,323/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -21803,7 +21803,7 @@
           <t>B2 | 342呎 (2房)
 $648万
 $18,940/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
       <c r="K16" s="20" t="inlineStr">
@@ -21811,7 +21811,7 @@
           <t>B3 | 263呎 (1房)
 $501万
 $19,032/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
       <c r="L16" s="20" t="inlineStr">
@@ -21819,7 +21819,7 @@
           <t>B5 | 263呎 (1房)
 $490万
 $18,627/呎
-(25年-03月-17日)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="M16" s="20" t="inlineStr">
@@ -21827,7 +21827,7 @@
           <t>B6 | 258呎 (1房)
 $476万
 $18,439/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="N16" s="20" t="inlineStr">
@@ -21835,7 +21835,7 @@
           <t>B7 | 200呎 (开放式)
 $381万
 $19,058/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="O16" s="20" t="inlineStr">
@@ -21843,7 +21843,7 @@
           <t>B8 | 262呎 (1房)
 $491万
 $18,728/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="P16" s="20" t="inlineStr">
@@ -21851,7 +21851,7 @@
           <t>B9 | 261呎 (1房)
 $491万
 $18,830/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -21866,7 +21866,7 @@
           <t>A1 | 349呎 (2房)
 $651万
 $18,642/呎
-(25年-03月-17日)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -21874,7 +21874,7 @@
           <t>A2 | 342呎 (2房)
 $619万
 $18,099/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -21882,7 +21882,7 @@
           <t>A3 | 263呎 (1房)
 $475万
 $18,046/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -21890,7 +21890,7 @@
           <t>A5 | 258呎 (1房)
 $479万
 $18,563/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -21898,7 +21898,7 @@
           <t>A6 | 200呎 (开放式)
 $376万
 $18,823/呎
-(25年-04月-10日)</t>
+(25年-04月-11日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -21906,7 +21906,7 @@
           <t>A7 | 262呎 (1房)
 $463万
 $17,676/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -21914,7 +21914,7 @@
           <t>A8 | 262呎 (1房)
 $495万
 $18,881/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -21922,7 +21922,7 @@
           <t>B1 | 351呎 (2房)
 $670万
 $19,084/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -21930,7 +21930,7 @@
           <t>B2 | 342呎 (2房)
 $647万
 $18,915/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="K17" s="20" t="inlineStr">
@@ -21938,7 +21938,7 @@
           <t>B3 | 263呎 (1房)
 $482万
 $18,344/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
       <c r="L17" s="20" t="inlineStr">
@@ -21946,7 +21946,7 @@
           <t>B5 | 263呎 (1房)
 $482万
 $18,344/呎
-(25年-03月-17日)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="M17" s="20" t="inlineStr">
@@ -21954,7 +21954,7 @@
           <t>B6 | 258呎 (1房)
 $469万
 $18,168/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="N17" s="20" t="inlineStr">
@@ -21962,7 +21962,7 @@
           <t>B7 | 200呎 (开放式)
 $369万
 $18,428/呎
-(25年-03月-27日)</t>
+(25年-03月-28日)</t>
         </is>
       </c>
       <c r="O17" s="20" t="inlineStr">
@@ -21970,7 +21970,7 @@
           <t>B8 | 262呎 (1房)
 $485万
 $18,495/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="P17" s="20" t="inlineStr">
@@ -21978,7 +21978,7 @@
           <t>B9 | 261呎 (1房)
 $485万
 $18,601/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
     </row>
@@ -21993,7 +21993,7 @@
           <t>A1 | 349呎 (2房)
 $641万
 $18,358/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -22001,7 +22001,7 @@
           <t>A2 | 342呎 (2房)
 $609万
 $17,819/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -22009,7 +22009,7 @@
           <t>A3 | 263呎 (1房)
 $466万
 $17,704/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -22017,7 +22017,7 @@
           <t>A5 | 258呎 (1房)
 $460万
 $17,843/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -22025,7 +22025,7 @@
           <t>A6 | 200呎 (开放式)
 $380万
 $18,997/呎
-(25年-03月-12日)</t>
+(25年-03月-13日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -22033,7 +22033,7 @@
           <t>A7 | 262呎 (1房)
 $458万
 $17,462/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -22041,7 +22041,7 @@
           <t>A8 | 262呎 (1房)
 $486万
 $18,537/呎
-(25年-03月-18日)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -22049,7 +22049,7 @@
           <t>B1 | 351呎 (2房)
 $661万
 $18,846/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -22057,7 +22057,7 @@
           <t>B2 | 342呎 (2房)
 $639万
 $18,687/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="K18" s="20" t="inlineStr">
@@ -22065,7 +22065,7 @@
           <t>B3 | 263呎 (1房)
 $473万
 $18,001/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="L18" s="20" t="inlineStr">
@@ -22073,7 +22073,7 @@
           <t>B5 | 263呎 (1房)
 $473万
 $18,001/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="M18" s="20" t="inlineStr">
@@ -22081,7 +22081,7 @@
           <t>B6 | 258呎 (1房)
 $460万
 $17,843/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="N18" s="20" t="inlineStr">
@@ -22089,7 +22089,7 @@
           <t>B7 | 200呎 (开放式)
 $366万
 $18,280/呎
-(25年-03月-30日)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
       <c r="O18" s="20" t="inlineStr">
@@ -22097,7 +22097,7 @@
           <t>B8 | 262呎 (1房)
 $468万
 $17,873/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="P18" s="20" t="inlineStr">
@@ -22105,7 +22105,7 @@
           <t>B9 | 261呎 (1房)
 $488万
 $18,710/呎
-(25年-03月-27日)</t>
+(25年-03月-28日)</t>
         </is>
       </c>
     </row>
@@ -22120,7 +22120,7 @@
           <t>A1 | 349呎 (2房)
 $629万
 $18,012/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -22128,7 +22128,7 @@
           <t>A2 | 342呎 (2房)
 $598万
 $17,485/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -22136,7 +22136,7 @@
           <t>A3 | 263呎 (1房)
 $457万
 $17,364/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -22144,7 +22144,7 @@
           <t>A5 | 258呎 (1房)
 $452万
 $17,516/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -22152,7 +22152,7 @@
           <t>A6 | 200呎 (开放式)
 $364万
 $18,188/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -22160,7 +22160,7 @@
           <t>A7 | 262呎 (1房)
 $452万
 $17,248/呎
-(25年-03月-18日)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -22168,7 +22168,7 @@
           <t>A8 | 262呎 (1房)
 $482万
 $18,390/呎
-(25年-03月-27日)</t>
+(25年-03月-28日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -22176,7 +22176,7 @@
           <t>B1 | 351呎 (2房)
 $651万
 $18,544/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -22184,7 +22184,7 @@
           <t>B2 | 342呎 (2房)
 $616万
 $18,013/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="K19" s="20" t="inlineStr">
@@ -22192,7 +22192,7 @@
           <t>B3 | 263呎 (1房)
 $464万
 $17,658/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="L19" s="20" t="inlineStr">
@@ -22200,7 +22200,7 @@
           <t>B5 | 263呎 (1房)
 $464万
 $17,658/呎
-(25年-03月-18日)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="M19" s="20" t="inlineStr">
@@ -22208,7 +22208,7 @@
           <t>B6 | 258呎 (1房)
 $452万
 $17,516/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="N19" s="20" t="inlineStr">
@@ -22216,7 +22216,7 @@
           <t>B7 | 200呎 (开放式)
 $371万
 $18,536/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="O19" s="20" t="inlineStr">
@@ -22224,7 +22224,7 @@
           <t>B8 | 262呎 (1房)
 $462万
 $17,641/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="P19" s="20" t="inlineStr">
@@ -22232,7 +22232,7 @@
           <t>B9 | 261呎 (1房)
 $481万
 $18,418/呎
-(25年-03月-27日)</t>
+(25年-03月-28日)</t>
         </is>
       </c>
     </row>
@@ -22247,7 +22247,7 @@
           <t>A1 | 349呎 (2房)
 $637万
 $18,246/呎
-(25年-02月-28日)</t>
+(25年-03月-01日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -22255,7 +22255,7 @@
           <t>A2 | 342呎 (2房)
 $606万
 $17,714/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -22263,7 +22263,7 @@
           <t>A3 | 263呎 (1房)
 $453万
 $17,206/呎
-(25年-02月-28日)</t>
+(25年-03月-01日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -22271,7 +22271,7 @@
           <t>A5 | 258呎 (1房)
 $444万
 $17,191/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -22279,7 +22279,7 @@
           <t>A6 | 200呎 (开放式)
 $363万
 $18,133/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -22287,7 +22287,7 @@
           <t>A7 | 262呎 (1房)
 $451万
 $17,223/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -22295,7 +22295,7 @@
           <t>A8 | 262呎 (1房)
 $468万
 $17,848/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -22303,7 +22303,7 @@
           <t>B1 | 351呎 (2房)
 $652万
 $18,583/呎
-(25年-04月-01日)</t>
+(25年-04月-02日)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -22311,7 +22311,7 @@
           <t>B2 | 342呎 (2房)
 $605万
 $17,679/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
       <c r="K20" s="20" t="inlineStr">
@@ -22319,7 +22319,7 @@
           <t>B3 | 263呎 (1房)
 $455万
 $17,316/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="L20" s="20" t="inlineStr">
@@ -22327,7 +22327,7 @@
           <t>B5 | 263呎 (1房)
 $455万
 $17,316/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="M20" s="20" t="inlineStr">
@@ -22335,7 +22335,7 @@
           <t>B6 | 258呎 (1房)
 $444万
 $17,191/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="N20" s="20" t="inlineStr">
@@ -22343,7 +22343,7 @@
           <t>B7 | 200呎 (开放式)
 $362万
 $18,082/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="O20" s="20" t="inlineStr">
@@ -22351,7 +22351,7 @@
           <t>B8 | 262呎 (1房)
 $456万
 $17,413/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="P20" s="20" t="inlineStr">
@@ -22359,7 +22359,7 @@
           <t>B9 | 261呎 (1房)
 $461万
 $17,681/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
     </row>
@@ -22374,7 +22374,7 @@
           <t>A1 | 349呎 (2房)
 $605万
 $17,324/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -22382,7 +22382,7 @@
           <t>A2 | 342呎 (2房)
 $575万
 $16,821/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -22390,7 +22390,7 @@
           <t>A3 | 263呎 (1房)
 $450万
 $17,098/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -22398,7 +22398,7 @@
           <t>A5 | 258呎 (1房)
 $437万
 $16,920/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -22406,7 +22406,7 @@
           <t>A6 | 200呎 (开放式)
 $358万
 $17,898/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -22414,7 +22414,7 @@
           <t>A7 | 262呎 (1房)
 $441万
 $16,823/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -22422,7 +22422,7 @@
           <t>A8 | 262呎 (1房)
 $459万
 $17,505/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -22430,7 +22430,7 @@
           <t>B1 | 351呎 (2房)
 $646万
 $18,410/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -22438,7 +22438,7 @@
           <t>B2 | 342呎 (2房)
 $593万
 $17,345/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="K21" s="20" t="inlineStr">
@@ -22446,7 +22446,7 @@
           <t>B3 | 263呎 (1房)
 $446万
 $16,976/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="L21" s="20" t="inlineStr">
@@ -22454,7 +22454,7 @@
           <t>B5 | 263呎 (1房)
 $446万
 $16,976/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="M21" s="20" t="inlineStr">
@@ -22462,7 +22462,7 @@
           <t>B6 | 258呎 (1房)
 $445万
 $17,233/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
       <c r="N21" s="20" t="inlineStr">
@@ -22470,7 +22470,7 @@
           <t>B7 | 200呎 (开放式)
 $357万
 $17,848/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="O21" s="20" t="inlineStr">
@@ -22478,7 +22478,7 @@
           <t>B8 | 262呎 (1房)
 $450万
 $17,185/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="P21" s="20" t="inlineStr">
@@ -22486,7 +22486,7 @@
           <t>B9 | 261呎 (1房)
 $452万
 $17,335/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
     </row>
@@ -22501,7 +22501,7 @@
           <t>A1 | 349呎 (2房)
 $595万
 $17,040/呎
-(25年-03月-27日)</t>
+(25年-03月-28日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -22509,7 +22509,7 @@
           <t>A2 | 342呎 (2房)
 $566万
 $16,541/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -22517,7 +22517,7 @@
           <t>A3 | 263呎 (1房)
 $433万
 $16,451/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -22525,7 +22525,7 @@
           <t>A5 | 258呎 (1房)
 $430万
 $16,649/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -22533,7 +22533,7 @@
           <t>A6 | 200呎 (开放式)
 $353万
 $17,668/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -22541,7 +22541,7 @@
           <t>A7 | 262呎 (1房)
 $443万
 $16,916/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -22549,7 +22549,7 @@
           <t>A8 | 262呎 (1房)
 $461万
 $17,594/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -22557,7 +22557,7 @@
           <t>B1 | 351呎 (2房)
 $615万
 $17,527/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -22565,7 +22565,7 @@
           <t>B2 | 342呎 (2房)
 $584万
 $17,068/呎
-(25年-02月-28日)</t>
+(25年-03月-01日)</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr">
@@ -22573,7 +22573,7 @@
           <t>B3 | 263呎 (1房)
 $448万
 $17,052/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="L22" s="20" t="inlineStr">
@@ -22581,7 +22581,7 @@
           <t>B5 | 263呎 (1房)
 $439万
 $16,689/呎
-(25年-03月-18日)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="M22" s="20" t="inlineStr">
@@ -22589,7 +22589,7 @@
           <t>B6 | 258呎 (1房)
 $433万
 $16,776/呎
-(25年-02月-28日)</t>
+(25年-03月-01日)</t>
         </is>
       </c>
       <c r="N22" s="20" t="inlineStr">
@@ -22597,7 +22597,7 @@
           <t>B7 | 200呎 (开放式)
 $433万
 $21,641/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
       <c r="O22" s="20" t="inlineStr">
@@ -22605,7 +22605,7 @@
           <t>B8 | 262呎 (1房)
 $454万
 $17,325/呎
-(25年-03月-27日)</t>
+(25年-03月-28日)</t>
         </is>
       </c>
       <c r="P22" s="20" t="inlineStr">
@@ -22613,7 +22613,7 @@
           <t>B9 | 261呎 (1房)
 $445万
 $17,046/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
     </row>
@@ -22628,7 +22628,7 @@
           <t>A1 | 349呎 (2房)
 $597万
 $17,117/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -22636,7 +22636,7 @@
           <t>A2 | 342呎 (2房)
 $554万
 $16,208/呎
-(25年-03月-18日)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -22644,7 +22644,7 @@
           <t>A3 | 263呎 (1房)
 $432万
 $16,430/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -22652,7 +22652,7 @@
           <t>A5 | 258呎 (1房)
 $421万
 $16,324/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -22660,7 +22660,7 @@
           <t>A6 | 200呎 (开放式)
 $348万
 $17,383/呎
-(25年-03月-31日)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -22668,7 +22668,7 @@
           <t>A7 | 262呎 (1房)
 $435万
 $16,586/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -22676,7 +22676,7 @@
           <t>A8 | 262呎 (1房)
 $444万
 $16,932/呎
-(25年-03月-27日)</t>
+(25年-03月-28日)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -22684,7 +22684,7 @@
           <t>B1 | 351呎 (2房)
 $605万
 $17,228/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -22692,7 +22692,7 @@
           <t>B2 | 342呎 (2房)
 $574万
 $16,791/呎
-(25年-02月-28日)</t>
+(25年-03月-01日)</t>
         </is>
       </c>
       <c r="K23" s="20" t="inlineStr">
@@ -22700,7 +22700,7 @@
           <t>B3 | 263呎 (1房)
 $441万
 $16,763/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="L23" s="20" t="inlineStr">
@@ -22708,7 +22708,7 @@
           <t>B5 | 263呎 (1房)
 $431万
 $16,406/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="M23" s="20" t="inlineStr">
@@ -22716,7 +22716,7 @@
           <t>B6 | 258呎 (1房)
 $421万
 $16,324/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="N23" s="20" t="inlineStr">
@@ -22724,7 +22724,7 @@
           <t>B7 | 200呎 (开放式)
 $346万
 $17,324/呎
-(25年-04月-02日)</t>
+(25年-04月-03日)</t>
         </is>
       </c>
       <c r="O23" s="20" t="inlineStr">
@@ -22732,7 +22732,7 @@
           <t>B8 | 262呎 (1房)
 $437万
 $16,669/呎
-(25年-03月-18日)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="P23" s="20" t="inlineStr">
@@ -22740,7 +22740,7 @@
           <t>B9 | 261呎 (1房)
 $437万
 $16,761/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
     </row>
@@ -22755,7 +22755,7 @@
           <t>A1 | 349呎 (2房)
 $577万
 $16,523/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -22763,7 +22763,7 @@
           <t>A2 | 342呎 (2房)
 $541万
 $15,820/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -22771,7 +22771,7 @@
           <t>A3 | 263呎 (1房)
 $410万
 $15,591/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -22779,7 +22779,7 @@
           <t>A5 | 258呎 (1房)
 $410万
 $15,890/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -22787,7 +22787,7 @@
           <t>A6 | 200呎 (开放式)
 $346万
 $17,296/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -22795,7 +22795,7 @@
           <t>A7 | 262呎 (1房)
 $417万
 $15,914/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -22803,7 +22803,7 @@
           <t>A8 | 262呎 (1房)
 $438万
 $16,704/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -22811,7 +22811,7 @@
           <t>B1 | 351呎 (2房)
 $601万
 $17,113/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -22819,7 +22819,7 @@
           <t>B2 | 342呎 (2房)
 $565万
 $16,514/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
       <c r="K24" s="20" t="inlineStr">
@@ -22827,7 +22827,7 @@
           <t>B3 | 263呎 (1房)
 $425万
 $16,175/呎
-(25年-03月-17日)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="L24" s="20" t="inlineStr">
@@ -22835,7 +22835,7 @@
           <t>B5 | 263呎 (1房)
 $425万
 $16,175/呎
-(25年-03月-16日)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="M24" s="20" t="inlineStr">
@@ -22843,7 +22843,7 @@
           <t>B6 | 258呎 (1房)
 $429万
 $16,632/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="N24" s="20" t="inlineStr">
@@ -22851,7 +22851,7 @@
           <t>B7 | 200呎 (开放式)
 $337万
 $16,872/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="O24" s="20" t="inlineStr">
@@ -22859,7 +22859,7 @@
           <t>B8 | 262呎 (1房)
 $446万
 $17,041/呎
-(25年-04月-01日)</t>
+(25年-04月-02日)</t>
         </is>
       </c>
       <c r="P24" s="20" t="inlineStr">
@@ -22867,7 +22867,7 @@
           <t>B9 | 261呎 (1房)
 $431万
 $16,532/呎
-(25年-03月-23日)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
     </row>
@@ -22882,7 +22882,7 @@
           <t>A1 | 311呎 (2房)
 $723万
 $23,241/呎
-(25年-04月-13日)</t>
+(25年-04月-14日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -22890,7 +22890,7 @@
           <t>A2 | 304呎 (2房)
 $656万
 $21,579/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -22898,7 +22898,7 @@
           <t>A3 | 225呎 (1房)
 $470万
 $20,881/呎
-(25年-04月-10日)</t>
+(25年-04月-11日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -22906,7 +22906,7 @@
           <t>A5 | 221呎 (1房)
 $465万
 $21,040/呎
-(25年-04月-10日)</t>
+(25年-04月-11日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -22914,7 +22914,7 @@
           <t>A6 | 178呎 (开放式)
 $452万
 $25,393/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -22922,7 +22922,7 @@
           <t>A7 | 224呎 (1房)
 $585万
 $26,116/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -22930,7 +22930,7 @@
           <t>A8 | 224呎 (1房)
 $633万
 $28,259/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -22938,7 +22938,7 @@
           <t>B1 | 313呎 (2房)
 $725万
 $23,163/呎
-(25年-07月-08日)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -22946,7 +22946,7 @@
           <t>B2 | 304呎 (2房)
 $660万
 $21,711/呎
-(25年-04月-02日)</t>
+(25年-04月-03日)</t>
         </is>
       </c>
       <c r="K25" s="20" t="inlineStr">
@@ -22954,7 +22954,7 @@
           <t>B3 | 225呎 (1房)
 $475万
 $21,111/呎
-(25年-06月-12日)</t>
+(25年-06月-13日)</t>
         </is>
       </c>
       <c r="L25" s="20" t="inlineStr">
@@ -22962,7 +22962,7 @@
           <t>B5 | 225呎 (1房)
 $470万
 $20,889/呎
-(25年-04月-10日)</t>
+(25年-04月-11日)</t>
         </is>
       </c>
       <c r="M25" s="20" t="inlineStr">
@@ -22970,7 +22970,7 @@
           <t>B6 | 220呎 (1房)
 $465万
 $21,136/呎
-(25年-04月-22日)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="N25" s="20" t="inlineStr">
@@ -22978,7 +22978,7 @@
           <t>B7 | 178呎 (开放式)
 $458万
 $25,730/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="O25" s="20" t="inlineStr">
@@ -22986,7 +22986,7 @@
           <t>B8 | 224呎 (1房)
 $520万
 $23,214/呎
-(25年-05月-07日)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
       <c r="P25" s="20" t="inlineStr">
@@ -22994,7 +22994,7 @@
           <t>B9 | 224呎 (1房)
 $618万
 $27,593/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-马头角-南首.xlsx
+++ b/files/九龙-马头角-南首.xlsx
@@ -2021,7 +2021,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -20525,7 +20525,7 @@
           <t>B1 | 351呎 (2房)
 $905万
 $25,795/呎
-(26年-07月-18日)</t>
+(26年-07月-31日)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">

--- a/files/九龙-马头角-南首.xlsx
+++ b/files/九龙-马头角-南首.xlsx
@@ -4873,7 +4873,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -20898,7 +20898,7 @@
           <t>A8 | 262呎 (1房)
 $650万
 $24,806/呎
-(26年-07月-14日)</t>
+(26年-08月-06日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">

--- a/files/九龙-马头角-南首.xlsx
+++ b/files/九龙-马头角-南首.xlsx
@@ -2145,7 +2145,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -20509,7 +20509,7 @@
           <t>A7 | 262呎 (1房)
 $611万
 $23,310/呎
-(26年-07月-19日)</t>
+(26年-08月-12日)</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">

--- a/files/九龙-马头角-南首.xlsx
+++ b/files/九龙-马头角-南首.xlsx
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -20396,7 +20396,7 @@
           <t>A7 | 262呎 (1房)
 $617万
 $23,565/呎
-(26年-07月-20日)</t>
+(26年-08月-14日)</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr"/>

--- a/files/九龙-马头角-南首.xlsx
+++ b/files/九龙-马头角-南首.xlsx
@@ -3008,34 +3008,34 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
-        <v>6797000</v>
+        <v>6661000</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>25943</v>
+        <v>25424</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="5" t="n">
-        <v>6661060</v>
+        <v>6661000</v>
       </c>
       <c r="L39" s="5" t="n">
         <v>25424</v>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -20239,7 +20239,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -20249,7 +20249,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -20639,12 +20639,12 @@
 (26年-07月-22日)</t>
         </is>
       </c>
-      <c r="H7" s="22" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>A8 | 262呎 (1房)
-$680万
-$25,943/呎
-(在售)</t>
+$666万
+$25,424/呎
+(26年-08月-24日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
